--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/COLORADO_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/COLORADO_2011.xlsx
@@ -2706,7 +2706,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C131">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C188">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C222">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C699">
@@ -20832,7 +20832,7 @@
       </c>
       <c r="B1138" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1138">
